--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60300057</v>
+        <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vinäs, 255 m NNV vägskälet, Ög</t>
+          <t>Vinäs, Vinäs, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532249</v>
+        <v>532572</v>
       </c>
       <c r="R2" t="n">
-        <v>6421754</v>
+        <v>6421675</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,74 +761,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskogsbryn mot grusväg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60300057</t>
+          <t>https://artportalen.se/Sighting/136952667</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72574930</v>
+        <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>97987</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>400 m VNV Vinäs, Ög</t>
+          <t>Skolenbäcken, Skolenbäcken, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532231</v>
+        <v>532378</v>
       </c>
       <c r="R3" t="n">
-        <v>6421828</v>
+        <v>6421670</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,25 +861,744 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136952478</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136952678</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vinäs, Vinäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532528</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6421644</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952678</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136952725</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skolenbäcken, Skolenbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532350</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6421636</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952725</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136952405</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skolenbäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532348</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6421685</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952405</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136952648</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vinäs, Vinäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532583</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6421694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952648</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>60300057</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vinäs, 255 m NNV vägskälet, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532249</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6421754</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrskogsbryn mot grusväg</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60300057</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>72574930</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>400 m VNV Vinäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>532231</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6421828</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/72574930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136952603</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vinäs, Vinäs, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>532600</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6421591</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952603</t>
         </is>
       </c>
     </row>
@@ -892,6 +1606,13 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>91660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27099-2023 artfynd.xlsx
+++ b/artfynd/A 27099-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952667</v>
       </c>
       <c r="B2" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136952478</v>
       </c>
       <c r="B3" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136952678</v>
       </c>
       <c r="B4" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136952725</v>
       </c>
       <c r="B5" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136952405</v>
       </c>
       <c r="B6" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136952648</v>
       </c>
       <c r="B7" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136952603</v>
       </c>
       <c r="B10" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
